--- a/Starbucks Variance Analysis & Rolling Forecast.xlsx
+++ b/Starbucks Variance Analysis & Rolling Forecast.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B4DB1AE-13D4-43DF-A167-6728821C626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F8476E5-DD6E-4562-9680-E880817D8A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget vs Actual" sheetId="1" r:id="rId1"/>
     <sheet name="Rolling Forecast" sheetId="2" r:id="rId2"/>
+    <sheet name="Business Case - Expansion" sheetId="3" r:id="rId3"/>
+    <sheet name="Business Case - Table" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>Starbucks FY2024 Budget vs Actual Variance Analysis</t>
   </si>
@@ -345,16 +347,445 @@
   </si>
   <si>
     <t>• As a result, even under the Upside Case (6% revenue growth), operating income margin improvement is modest, reflecting the structural cost pressure identified in the prior analysis</t>
+  </si>
+  <si>
+    <t>Should Starbucks Open 50 New Stores? — ROI &amp; Payback Analysis</t>
+  </si>
+  <si>
+    <t>Business case evaluating a new store expansion initiative</t>
+  </si>
+  <si>
+    <t>Number of New Stores</t>
+  </si>
+  <si>
+    <t>Investment per Store</t>
+  </si>
+  <si>
+    <t>Year 1 Revenue per Store</t>
+  </si>
+  <si>
+    <t>Store-Level Operating Margin</t>
+  </si>
+  <si>
+    <t>Total Initial Investment</t>
+  </si>
+  <si>
+    <t>Total Year 1 Revenue</t>
+  </si>
+  <si>
+    <t>Total Year 1 Operating Profit</t>
+  </si>
+  <si>
+    <t>Payback Period (Year)</t>
+  </si>
+  <si>
+    <t>Annual Revenue Growth (as stores mature)</t>
+  </si>
+  <si>
+    <t>Discount Rate (for NPV)</t>
+  </si>
+  <si>
+    <t>5-Year Projection &amp; NPV Analysis</t>
+  </si>
+  <si>
+    <t>Linked to Business Case - Expansion assumptions</t>
+  </si>
+  <si>
+    <t>Store Level Operating Margin</t>
+  </si>
+  <si>
+    <t>Annual Revenue Growth</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>Year 1 Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Operating Profit</t>
+  </si>
+  <si>
+    <t>Discount Factor</t>
+  </si>
+  <si>
+    <t>Present Value of Profit</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>NPV (5-Year)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Expansion scenario:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 50 new company-operated stores</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Initial investment ($500K/store) and Year 1 revenue ($1.2M/store)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>third-party industry data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for coffee retail store economics (Starbucks does not publicly disclose per-store financials)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Store-level operating margin (17%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>approximated from</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Starbucks' FY2023 company-wide operating margin (16.3%), used as a reasonable proxy since store-level margin data isn't public</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Annual revenue growth (5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reflects a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>general assumption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for store maturation, not company-specific historical data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Discount rate (10%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — same rate used in the Microsoft DCF valuation, kept consistent across projects</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Results &amp; Recommendation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Payback Period:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2.45 years — the initial $25 million investment is recovered from operating profit in under 2.5 years</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5-Year NPV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: +$17.3 million — after discounting future profits back to present value and subtracting the initial investment, the expansion generates a net positive return of approximately $17.3 million</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommendation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Proceed with the expansion. Both metrics point the same direction — a short payback period signals low risk (capital is recovered quickly), while a strongly positive NPV confirms the investment creates meaningful long-term value beyond simply recovering its cost</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This analysis uses industry-average unit economics rather than site-specific data (e.g., real estate costs, local market saturation, cannibalization of existing nearby stores), which would materially affect actual results for any specific expansion decision</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,8 +866,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +939,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -470,11 +954,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -508,11 +1033,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
@@ -551,7 +1110,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{979D77DA-2DDC-4C9F-A169-FF9535C03E66}" name="Table2" displayName="Table2" ref="A4:G18" totalsRowShown="0" headerRowDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{979D77DA-2DDC-4C9F-A169-FF9535C03E66}" name="Table2" displayName="Table2" ref="A4:G18" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A4:G18" xr:uid="{979D77DA-2DDC-4C9F-A169-FF9535C03E66}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -565,14 +1124,14 @@
     <tableColumn id="1" xr3:uid="{AFD8D492-EAED-45A9-9F57-5EC08019FB4D}" name="Line Item"/>
     <tableColumn id="2" xr3:uid="{A608B9FA-8091-4276-B5D7-B6A8AA5A2CBB}" name="Budget (FY2024)"/>
     <tableColumn id="3" xr3:uid="{7F508EA7-A56F-45CC-A753-3A09A71DEF1C}" name="Actual (FY2024)"/>
-    <tableColumn id="4" xr3:uid="{5F2CB031-F4B6-4D64-8339-D2F17D8A5A35}" name="Variance ($)" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{5F2CB031-F4B6-4D64-8339-D2F17D8A5A35}" name="Variance ($)" dataDxfId="10">
       <calculatedColumnFormula>C5-B5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{E59A6950-5691-40C9-8B8D-935A31CA7E74}" name="Variance (%)" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{E59A6950-5691-40C9-8B8D-935A31CA7E74}" name="Variance (%)" dataDxfId="9">
       <calculatedColumnFormula>(C5-B5)/B5</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{24C0A21B-8D5A-4735-8B86-3E0F3C2C767A}" name="FY2023 Actual"/>
-    <tableColumn id="7" xr3:uid="{9AA506D3-ADA5-4180-8023-00E0E9C2F526}" name="% of Revenue" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{9AA506D3-ADA5-4180-8023-00E0E9C2F526}" name="% of Revenue" dataDxfId="8">
       <calculatedColumnFormula>F5/$F$8</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -592,11 +1151,37 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E3676DE-45C7-4ED1-847E-021C1178148E}" name="Line Item"/>
     <tableColumn id="2" xr3:uid="{DC20FFB3-7F80-4609-8FAB-ADCBFCB973AF}" name="FY2024 Actual (Base)"/>
-    <tableColumn id="3" xr3:uid="{30E339C5-8695-4EA4-BA29-50F83FBA9F46}" name="Base Case" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{A88D3196-9974-4CF4-84B1-51AC0460BA14}" name="Upside Case" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{37B618FF-1F76-4E69-906B-B6A025EEAB4F}" name="Downside Case" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{30E339C5-8695-4EA4-BA29-50F83FBA9F46}" name="Base Case" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{A88D3196-9974-4CF4-84B1-51AC0460BA14}" name="Upside Case" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{37B618FF-1F76-4E69-906B-B6A025EEAB4F}" name="Downside Case" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{88BA5B35-14C5-4CA8-8B6C-9F3B3D712FCF}" name="Table3" displayName="Table3" ref="A10:E15" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A10:E15" xr:uid="{88BA5B35-14C5-4CA8-8B6C-9F3B3D712FCF}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2896465C-C579-40E3-856F-1C407AE1CFCF}" name="Year "/>
+    <tableColumn id="2" xr3:uid="{74D9B6DE-B19F-41ED-A30E-ED795142AF9C}" name="Revenue" dataDxfId="3">
+      <calculatedColumnFormula>B10*(1+$B$5)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{A78AD196-D214-42FD-AEC2-3F865A1DCF92}" name="Operating Profit" dataDxfId="2">
+      <calculatedColumnFormula>B11*$B$4</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{B5D803C3-EF2F-488C-A2D0-B9A57AFF7160}" name="Discount Factor" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{7B6EB7F3-DA5E-4ABD-B96B-472787C885D3}" name="Present Value of Profit" dataDxfId="0">
+      <calculatedColumnFormula>C11*D11</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1738,4 +2323,379 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23634A3-E6F6-4228-9791-D42876AC6865}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21">
+      <c r="A1" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75">
+      <c r="A2" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="24">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="15">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="24"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="24">
+        <f>B4*B5</f>
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="24">
+        <f>B4*B6</f>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="24">
+        <f>B7*B10</f>
+        <v>10200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="25">
+        <f>B9/B11</f>
+        <v>2.4509803921568629</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="15">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD4A14D-BC4C-49A8-A1D2-281CAD454ED4}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="23.25">
+      <c r="A1" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="31">
+        <f>'Business Case - Expansion'!B7</f>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="31">
+        <f>'Business Case - Expansion'!B16</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="31">
+        <f>'Business Case - Expansion'!B17</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="32">
+        <f>'Business Case - Expansion'!B9</f>
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="32">
+        <f>'Business Case - Expansion'!B10</f>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="24">
+        <f>B8</f>
+        <v>60000000</v>
+      </c>
+      <c r="C11" s="24">
+        <f>B11*B4</f>
+        <v>10200000</v>
+      </c>
+      <c r="D11" s="25">
+        <f>1/(1+$B$6)^1</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="E11" s="23">
+        <f>C11*D11</f>
+        <v>9272727.2727272715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="24">
+        <f>B11*(1+$B$5)</f>
+        <v>63000000</v>
+      </c>
+      <c r="C12" s="24">
+        <f>B12*$B$4</f>
+        <v>10710000</v>
+      </c>
+      <c r="D12" s="25">
+        <f>1/(1+$B$6)^2</f>
+        <v>0.82644628099173545</v>
+      </c>
+      <c r="E12" s="23">
+        <f t="shared" ref="E12:E15" si="0">C12*D12</f>
+        <v>8851239.6694214866</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" ref="B13:B15" si="1">B12*(1+$B$5)</f>
+        <v>66150000</v>
+      </c>
+      <c r="C13" s="24">
+        <f t="shared" ref="C13:C15" si="2">B13*$B$4</f>
+        <v>11245500</v>
+      </c>
+      <c r="D13" s="25">
+        <f>1/(1+$B$6)^3</f>
+        <v>0.75131480090157754</v>
+      </c>
+      <c r="E13" s="23">
+        <f t="shared" si="0"/>
+        <v>8448910.5935386904</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="24">
+        <f t="shared" si="1"/>
+        <v>69457500</v>
+      </c>
+      <c r="C14" s="24">
+        <f t="shared" si="2"/>
+        <v>11807775</v>
+      </c>
+      <c r="D14" s="25">
+        <f>1/(1+$B$6)^4</f>
+        <v>0.68301345536507052</v>
+      </c>
+      <c r="E14" s="23">
+        <f t="shared" si="0"/>
+        <v>8064869.202923296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="1"/>
+        <v>72930375</v>
+      </c>
+      <c r="C15" s="24">
+        <f t="shared" si="2"/>
+        <v>12398163.75</v>
+      </c>
+      <c r="D15" s="25">
+        <f>1/(1+$B$6)^5</f>
+        <v>0.62092132305915493</v>
+      </c>
+      <c r="E15" s="23">
+        <f t="shared" si="0"/>
+        <v>7698284.2391540539</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="29">
+        <f>SUM(E11:E15)-B7</f>
+        <v>17336030.9777648</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18.75">
+      <c r="A20" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="8"/>
+    </row>
+    <row r="27" spans="1:2" ht="18.75">
+      <c r="A27" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>